--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
 dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}proc-mii-1:Falls die Prozedur per OPS kodiert wird, MUSS eine SNOMED-CT kodierte Category abgebildet werden {code.coding.where(system = 'http://fhir.de/CodeSystem/bfarm/ops').exists() implies category.coding.where(system = 'http://snomed.info/sct').exists()}</t>
   </si>
   <si>
-    <t>KR-Stoma</t>
+    <t>KR7</t>
   </si>
   <si>
     <t>Procedure.id</t>
@@ -767,6 +767,9 @@
   </si>
   <si>
     <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/ValueSet/mii-vs-onko-krk-stoma-status-reason</t>
+  </si>
+  <si>
+    <t>KR7 (Komponente)</t>
   </si>
   <si>
     <t>Procedure.category</t>
@@ -1221,9 +1224,6 @@
   </si>
   <si>
     <t>Datum der präoperativen Stoma-Markierung</t>
-  </si>
-  <si>
-    <t>KR-Stoma.1</t>
   </si>
   <si>
     <t>Procedure.performed[x]:performedPeriod</t>
@@ -4757,7 +4757,7 @@
         <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27">
@@ -4860,15 +4860,15 @@
         <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>74</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4894,13 +4894,13 @@
         <v>234</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4929,10 +4929,10 @@
         <v>149</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>74</v>
@@ -4950,7 +4950,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5073,10 +5073,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5178,10 +5178,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5207,16 +5207,16 @@
         <v>137</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>74</v>
@@ -5226,7 +5226,7 @@
         <v>74</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>74</v>
@@ -5253,7 +5253,7 @@
         <v>74</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
@@ -5263,7 +5263,7 @@
         <v>110</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -5283,13 +5283,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>74</v>
@@ -5314,16 +5314,16 @@
         <v>137</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>74</v>
@@ -5333,7 +5333,7 @@
         <v>74</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>74</v>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -5370,7 +5370,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -5390,10 +5390,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5493,10 +5493,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5598,10 +5598,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5627,16 +5627,16 @@
         <v>125</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>74</v>
@@ -5685,7 +5685,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -5705,10 +5705,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5734,13 +5734,13 @@
         <v>98</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5790,7 +5790,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -5810,10 +5810,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5839,16 +5839,16 @@
         <v>159</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>74</v>
@@ -5897,7 +5897,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
@@ -5917,10 +5917,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5946,16 +5946,16 @@
         <v>98</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>74</v>
@@ -6004,7 +6004,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -6024,10 +6024,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6050,19 +6050,19 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>74</v>
@@ -6111,7 +6111,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -6131,10 +6131,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6160,16 +6160,16 @@
         <v>98</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>74</v>
@@ -6218,7 +6218,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -6238,14 +6238,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6267,16 +6267,16 @@
         <v>234</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>74</v>
@@ -6304,10 +6304,10 @@
         <v>149</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>74</v>
@@ -6325,7 +6325,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6337,7 +6337,7 @@
         <v>95</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>74</v>
@@ -6345,10 +6345,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6448,10 +6448,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6553,10 +6553,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6582,16 +6582,16 @@
         <v>137</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>74</v>
@@ -6601,7 +6601,7 @@
         <v>74</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>74</v>
@@ -6628,7 +6628,7 @@
         <v>74</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
@@ -6638,7 +6638,7 @@
         <v>110</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -6658,13 +6658,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>74</v>
@@ -6686,19 +6686,19 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>74</v>
@@ -6708,7 +6708,7 @@
         <v>74</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>74</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>74</v>
@@ -6745,7 +6745,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -6765,10 +6765,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6868,10 +6868,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6973,13 +6973,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="B48" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="C48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>103</v>
@@ -7001,13 +7001,13 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>107</v>
@@ -7080,10 +7080,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7109,23 +7109,23 @@
         <v>125</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>74</v>
@@ -7167,7 +7167,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
@@ -7187,10 +7187,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7216,13 +7216,13 @@
         <v>98</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7272,7 +7272,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -7292,10 +7292,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7321,16 +7321,16 @@
         <v>159</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>74</v>
@@ -7343,7 +7343,7 @@
         <v>74</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>74</v>
@@ -7379,7 +7379,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -7391,7 +7391,7 @@
         <v>95</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>74</v>
@@ -7399,10 +7399,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7428,16 +7428,16 @@
         <v>98</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
@@ -7486,7 +7486,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7532,19 +7532,19 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>74</v>
@@ -7593,7 +7593,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -7613,13 +7613,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>74</v>
@@ -7644,16 +7644,16 @@
         <v>137</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>74</v>
@@ -7663,7 +7663,7 @@
         <v>74</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>74</v>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>74</v>
@@ -7700,7 +7700,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -7720,10 +7720,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7823,10 +7823,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7928,10 +7928,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7957,16 +7957,16 @@
         <v>125</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>74</v>
@@ -8015,7 +8015,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -8035,10 +8035,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8064,13 +8064,13 @@
         <v>98</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8120,7 +8120,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
@@ -8140,10 +8140,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8169,16 +8169,16 @@
         <v>159</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>74</v>
@@ -8227,7 +8227,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -8247,10 +8247,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8276,16 +8276,16 @@
         <v>98</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>74</v>
@@ -8334,7 +8334,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -8354,10 +8354,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8380,19 +8380,19 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>74</v>
@@ -8441,7 +8441,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -8461,10 +8461,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8490,16 +8490,16 @@
         <v>98</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>74</v>
@@ -8548,7 +8548,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
@@ -8568,14 +8568,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8594,13 +8594,13 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>218</v>
@@ -8653,7 +8653,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -8673,10 +8673,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8699,16 +8699,16 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8758,7 +8758,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -8778,10 +8778,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8804,16 +8804,16 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8851,17 +8851,17 @@
         <v>74</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AC65" s="2"/>
       <c r="AD65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -8881,13 +8881,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>74</v>
@@ -8909,16 +8909,16 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8968,7 +8968,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
@@ -8983,7 +8983,7 @@
         <v>96</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>382</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" hidden="true">
@@ -8991,7 +8991,7 @@
         <v>383</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C67" t="s" s="2">
         <v>384</v>
@@ -9025,7 +9025,7 @@
         <v>387</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9075,7 +9075,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
@@ -9758,7 +9758,7 @@
         <v>408</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>409</v>
@@ -10703,16 +10703,16 @@
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>74</v>
@@ -10759,7 +10759,7 @@
         <v>110</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>75</v>
@@ -10810,16 +10810,16 @@
         <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>74</v>
@@ -10868,7 +10868,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>75</v>
@@ -11125,16 +11125,16 @@
         <v>125</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>74</v>
@@ -11183,7 +11183,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>75</v>
@@ -11232,13 +11232,13 @@
         <v>98</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11288,7 +11288,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
@@ -11337,16 +11337,16 @@
         <v>159</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>74</v>
@@ -11395,7 +11395,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -11444,16 +11444,16 @@
         <v>98</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>74</v>
@@ -11502,7 +11502,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>75</v>
@@ -11548,19 +11548,19 @@
         <v>84</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>74</v>
@@ -11609,7 +11609,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>75</v>
@@ -11658,16 +11658,16 @@
         <v>98</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>74</v>
@@ -11716,7 +11716,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>75</v>
@@ -12193,7 +12193,7 @@
         <v>490</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -12821,7 +12821,7 @@
         <v>506</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$145</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5211" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5251" uniqueCount="664">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1309,6 +1309,9 @@
     <t>Procedure.code.coding.extension.value[x].code</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
   </si>
   <si>
@@ -1829,6 +1832,22 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding</t>
@@ -2385,7 +2404,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN144"/>
+  <dimension ref="A1:AN145"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -4687,7 +4706,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>115</v>
@@ -4913,7 +4932,7 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>99</v>
@@ -9465,7 +9484,7 @@
         <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>115</v>
@@ -9805,7 +9824,7 @@
         <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>115</v>
@@ -10029,7 +10048,7 @@
         <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>99</v>
@@ -10255,7 +10274,7 @@
         <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>115</v>
@@ -10371,7 +10390,7 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>99</v>
@@ -10485,7 +10504,7 @@
         <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>99</v>
@@ -10539,7 +10558,9 @@
       <c r="M72" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N72" s="2"/>
+      <c r="N72" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="O72" t="s" s="2">
         <v>246</v>
       </c>
@@ -10599,7 +10620,7 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>99</v>
@@ -10619,10 +10640,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10653,7 +10674,9 @@
       <c r="M73" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N73" s="2"/>
+      <c r="N73" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="O73" t="s" s="2">
         <v>253</v>
       </c>
@@ -10713,7 +10736,7 @@
         <v>87</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>99</v>
@@ -10733,10 +10756,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10829,7 +10852,7 @@
         <v>87</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>99</v>
@@ -10849,10 +10872,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10878,7 +10901,7 @@
         <v>128</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>229</v>
@@ -10894,7 +10917,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>77</v>
@@ -10945,7 +10968,7 @@
         <v>87</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>99</v>
@@ -10965,10 +10988,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10994,10 +11017,10 @@
         <v>101</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>239</v>
@@ -11059,7 +11082,7 @@
         <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>99</v>
@@ -11079,10 +11102,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11108,12 +11131,14 @@
         <v>162</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M77" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N77" s="2"/>
+      <c r="N77" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="O77" t="s" s="2">
         <v>246</v>
       </c>
@@ -11128,7 +11153,7 @@
         <v>77</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>77</v>
@@ -11173,10 +11198,10 @@
         <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
@@ -11193,10 +11218,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11227,7 +11252,9 @@
       <c r="M78" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N78" s="2"/>
+      <c r="N78" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="O78" t="s" s="2">
         <v>253</v>
       </c>
@@ -11287,7 +11314,7 @@
         <v>87</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>99</v>
@@ -11307,10 +11334,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11403,7 +11430,7 @@
         <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>99</v>
@@ -11423,7 +11450,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>375</v>
@@ -11492,7 +11519,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>77</v>
@@ -11539,7 +11566,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>385</v>
@@ -11651,7 +11678,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>387</v>
@@ -11765,10 +11792,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11881,10 +11908,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11995,10 +12022,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12109,10 +12136,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12223,10 +12250,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12339,10 +12366,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12455,14 +12482,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12481,13 +12508,13 @@
         <v>88</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12538,7 +12565,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>87</v>
@@ -12556,21 +12583,21 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12679,10 +12706,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12793,10 +12820,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12822,13 +12849,13 @@
         <v>101</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12878,7 +12905,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12887,7 +12914,7 @@
         <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>99</v>
@@ -12907,10 +12934,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12936,13 +12963,13 @@
         <v>128</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12971,10 +12998,10 @@
         <v>144</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>77</v>
@@ -12992,7 +13019,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13021,10 +13048,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13050,13 +13077,13 @@
         <v>271</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13106,7 +13133,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13135,10 +13162,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13164,13 +13191,13 @@
         <v>101</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13220,7 +13247,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13249,10 +13276,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13275,16 +13302,16 @@
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13334,7 +13361,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13352,21 +13379,21 @@
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13475,10 +13502,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13589,10 +13616,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13618,13 +13645,13 @@
         <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13674,7 +13701,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13683,7 +13710,7 @@
         <v>87</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>99</v>
@@ -13703,10 +13730,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13732,13 +13759,13 @@
         <v>128</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13767,10 +13794,10 @@
         <v>144</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>77</v>
@@ -13788,7 +13815,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13817,10 +13844,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13846,13 +13873,13 @@
         <v>271</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13902,7 +13929,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13931,10 +13958,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13960,13 +13987,13 @@
         <v>101</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14016,7 +14043,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14045,10 +14072,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14074,13 +14101,13 @@
         <v>206</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14118,17 +14145,17 @@
         <v>77</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14146,24 +14173,24 @@
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>77</v>
@@ -14188,13 +14215,13 @@
         <v>206</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14244,7 +14271,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14262,24 +14289,24 @@
         <v>84</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>77</v>
@@ -14301,16 +14328,16 @@
         <v>88</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14360,7 +14387,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14378,21 +14405,21 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14415,13 +14442,13 @@
         <v>88</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14472,7 +14499,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14493,7 +14520,7 @@
         <v>77</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>77</v>
@@ -14501,10 +14528,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14527,13 +14554,13 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14584,7 +14611,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14605,7 +14632,7 @@
         <v>77</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>77</v>
@@ -14613,10 +14640,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14639,13 +14666,13 @@
         <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14696,7 +14723,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14714,7 +14741,7 @@
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>77</v>
@@ -14725,10 +14752,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14837,10 +14864,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14951,14 +14978,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -14980,10 +15007,10 @@
         <v>107</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>110</v>
@@ -15038,7 +15065,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15067,10 +15094,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15096,14 +15123,14 @@
         <v>311</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>77</v>
@@ -15131,10 +15158,10 @@
         <v>152</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>77</v>
@@ -15152,7 +15179,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15170,21 +15197,21 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15207,17 +15234,17 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>77</v>
@@ -15266,7 +15293,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>87</v>
@@ -15284,21 +15311,21 @@
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15321,17 +15348,17 @@
         <v>77</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>77</v>
@@ -15380,7 +15407,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15409,10 +15436,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15435,17 +15462,17 @@
         <v>88</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>77</v>
@@ -15494,7 +15521,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15515,7 +15542,7 @@
         <v>77</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>77</v>
@@ -15523,10 +15550,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15552,13 +15579,13 @@
         <v>311</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15587,10 +15614,10 @@
         <v>152</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>77</v>
@@ -15608,7 +15635,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15626,10 +15653,10 @@
         <v>77</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>77</v>
@@ -15637,10 +15664,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15663,16 +15690,16 @@
         <v>88</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15722,7 +15749,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -15740,10 +15767,10 @@
         <v>77</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>77</v>
@@ -15751,10 +15778,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15780,13 +15807,13 @@
         <v>311</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15815,10 +15842,10 @@
         <v>152</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>77</v>
@@ -15836,7 +15863,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15860,15 +15887,15 @@
         <v>77</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15977,10 +16004,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16091,12 +16118,14 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="C121" s="2"/>
+      <c r="C121" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="D121" t="s" s="2">
         <v>77</v>
       </c>
@@ -16105,32 +16134,28 @@
         <v>78</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>140</v>
+        <v>583</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>327</v>
+        <v>584</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>77</v>
       </c>
@@ -16166,17 +16191,19 @@
         <v>77</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AC121" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>333</v>
+        <v>114</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16188,7 +16215,7 @@
         <v>77</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>77</v>
@@ -16200,19 +16227,17 @@
         <v>77</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>334</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>583</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>77</v>
       </c>
@@ -16221,7 +16246,7 @@
         <v>78</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>88</v>
@@ -16236,10 +16261,10 @@
         <v>140</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>329</v>
@@ -16282,16 +16307,14 @@
         <v>77</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF122" t="s" s="2">
         <v>333</v>
@@ -16321,14 +16344,16 @@
         <v>334</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="C123" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="D123" t="s" s="2">
         <v>77</v>
       </c>
@@ -16340,25 +16365,29 @@
         <v>87</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>102</v>
+        <v>337</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P123" t="s" s="2">
         <v>77</v>
       </c>
@@ -16406,19 +16435,19 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>104</v>
+        <v>333</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>77</v>
@@ -16430,26 +16459,26 @@
         <v>77</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>77</v>
+        <v>334</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>77</v>
@@ -16461,17 +16490,15 @@
         <v>77</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>77</v>
@@ -16508,31 +16535,31 @@
         <v>77</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>77</v>
@@ -16547,48 +16574,46 @@
         <v>77</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>229</v>
+        <v>109</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>77</v>
       </c>
@@ -16597,7 +16622,7 @@
         <v>77</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>77</v>
@@ -16624,31 +16649,31 @@
         <v>77</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>233</v>
+        <v>114</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>77</v>
@@ -16660,15 +16685,15 @@
         <v>77</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16676,7 +16701,7 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>87</v>
@@ -16691,18 +16716,20 @@
         <v>88</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
       </c>
@@ -16711,7 +16738,7 @@
         <v>77</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>77</v>
@@ -16750,7 +16777,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16774,15 +16801,15 @@
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16790,7 +16817,7 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>87</v>
@@ -16805,18 +16832,18 @@
         <v>88</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N127" s="2"/>
-      <c r="O127" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>77</v>
       </c>
@@ -16864,7 +16891,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -16888,15 +16915,15 @@
         <v>77</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16904,13 +16931,13 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>77</v>
@@ -16919,17 +16946,17 @@
         <v>88</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>77</v>
@@ -16978,7 +17005,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17002,15 +17029,15 @@
         <v>77</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17033,19 +17060,17 @@
         <v>88</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>77</v>
@@ -17094,7 +17119,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17118,15 +17143,15 @@
         <v>77</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17149,19 +17174,19 @@
         <v>88</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>356</v>
+        <v>259</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>357</v>
+        <v>260</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>358</v>
+        <v>261</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>359</v>
+        <v>262</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>77</v>
@@ -17210,7 +17235,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>360</v>
+        <v>263</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17234,15 +17259,15 @@
         <v>77</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>361</v>
+        <v>264</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17265,18 +17290,20 @@
         <v>88</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>311</v>
+        <v>101</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>600</v>
+        <v>356</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>601</v>
+        <v>357</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="O131" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>77</v>
       </c>
@@ -17300,13 +17327,13 @@
         <v>77</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>603</v>
+        <v>77</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>604</v>
+        <v>77</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>77</v>
@@ -17324,7 +17351,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>599</v>
+        <v>360</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17348,7 +17375,7 @@
         <v>77</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
     </row>
     <row r="132" hidden="true">
@@ -17367,7 +17394,7 @@
         <v>78</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>77</v>
@@ -17376,19 +17403,19 @@
         <v>77</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -17414,13 +17441,13 @@
         <v>77</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>77</v>
+        <v>609</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>77</v>
+        <v>610</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>77</v>
@@ -17444,7 +17471,7 @@
         <v>78</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>77</v>
@@ -17467,10 +17494,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17493,16 +17520,16 @@
         <v>77</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>311</v>
+        <v>612</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17528,13 +17555,13 @@
         <v>77</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>614</v>
+        <v>77</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>615</v>
+        <v>77</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>77</v>
@@ -17552,7 +17579,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17607,18 +17634,18 @@
         <v>77</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="M134" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="N134" s="2"/>
-      <c r="O134" t="s" s="2">
-        <v>620</v>
-      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>77</v>
       </c>
@@ -17642,13 +17669,13 @@
         <v>77</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>77</v>
+        <v>620</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>77</v>
+        <v>621</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>77</v>
@@ -17695,10 +17722,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17721,16 +17748,18 @@
         <v>77</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>311</v>
+        <v>623</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
+      <c r="O135" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="P135" t="s" s="2">
         <v>77</v>
       </c>
@@ -17754,13 +17783,13 @@
         <v>77</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>624</v>
+        <v>77</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>625</v>
+        <v>77</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>77</v>
@@ -17778,7 +17807,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17805,12 +17834,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17824,7 +17853,7 @@
         <v>79</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>77</v>
@@ -17833,7 +17862,7 @@
         <v>77</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>627</v>
+        <v>311</v>
       </c>
       <c r="L136" t="s" s="2">
         <v>628</v>
@@ -17866,13 +17895,13 @@
         <v>77</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>77</v>
+        <v>630</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>77</v>
+        <v>631</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>77</v>
@@ -17890,7 +17919,7 @@
         <v>77</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -17908,16 +17937,16 @@
         <v>77</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>630</v>
+        <v>77</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>631</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
         <v>632</v>
       </c>
@@ -17936,7 +17965,7 @@
         <v>79</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>77</v>
@@ -17945,13 +17974,13 @@
         <v>77</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>519</v>
+        <v>633</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -18020,21 +18049,21 @@
         <v>77</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>77</v>
+        <v>636</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>77</v>
+        <v>637</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18045,7 +18074,7 @@
         <v>78</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>77</v>
@@ -18057,13 +18086,13 @@
         <v>77</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>101</v>
+        <v>520</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>102</v>
+        <v>639</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>103</v>
+        <v>640</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -18114,19 +18143,19 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>104</v>
+        <v>638</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>77</v>
@@ -18143,21 +18172,21 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>77</v>
@@ -18169,17 +18198,15 @@
         <v>77</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>77</v>
@@ -18228,19 +18255,19 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>77</v>
@@ -18257,14 +18284,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>526</v>
+        <v>106</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18277,26 +18304,24 @@
         <v>77</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K140" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>527</v>
+        <v>108</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>528</v>
+        <v>109</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="O140" t="s" s="2">
-        <v>268</v>
-      </c>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>77</v>
       </c>
@@ -18344,7 +18369,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>529</v>
+        <v>114</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18373,42 +18398,46 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>77</v>
+        <v>527</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I141" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>311</v>
+        <v>107</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>639</v>
+        <v>528</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
+        <v>529</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>77</v>
       </c>
@@ -18432,13 +18461,13 @@
         <v>77</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>641</v>
+        <v>77</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>642</v>
+        <v>77</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>77</v>
@@ -18456,19 +18485,19 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>638</v>
+        <v>530</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>77</v>
@@ -18485,10 +18514,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18496,7 +18525,7 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>87</v>
@@ -18511,7 +18540,7 @@
         <v>77</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>644</v>
+        <v>311</v>
       </c>
       <c r="L142" t="s" s="2">
         <v>645</v>
@@ -18544,13 +18573,13 @@
         <v>77</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>77</v>
+        <v>647</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>77</v>
+        <v>648</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>77</v>
@@ -18568,10 +18597,10 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>87</v>
@@ -18597,10 +18626,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18608,10 +18637,10 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>77</v>
@@ -18623,20 +18652,16 @@
         <v>77</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="O143" t="s" s="2">
         <v>652</v>
       </c>
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>77</v>
       </c>
@@ -18684,13 +18709,13 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>77</v>
@@ -18739,18 +18764,20 @@
         <v>77</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>311</v>
+        <v>654</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="O144" s="2"/>
+        <v>657</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>658</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>77</v>
       </c>
@@ -18774,13 +18801,13 @@
         <v>77</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>656</v>
+        <v>77</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>657</v>
+        <v>77</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>77</v>
@@ -18825,8 +18852,122 @@
         <v>77</v>
       </c>
     </row>
+    <row r="145" hidden="true">
+      <c r="A145" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="O145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN144">
+  <autoFilter ref="A1:AN145">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18836,7 +18977,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI143">
+  <conditionalFormatting sqref="A2:AI144">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-krk-stoma-markierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
